--- a/Content/Data/PlayerBaseStat.xlsx
+++ b/Content/Data/PlayerBaseStat.xlsx
@@ -460,13 +460,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,6 +490,21 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>MaxMana</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ManaRegen</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>JumpPower</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Comment</t>
         </is>
       </c>
@@ -509,6 +527,21 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>[int]</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[float]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>[float]</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>[string]</t>
         </is>
       </c>
@@ -530,6 +563,21 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>최대 마나</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>초당 마나 회복량</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>점프력</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기획 메모(변환시 제외)</t>
         </is>
@@ -545,14 +593,23 @@
       <c r="C4" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>기본 스탯</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="6">
     <dataValidation sqref="A4:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="Hp는 0보다 커야 합니다." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
@@ -560,6 +617,15 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="C4:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="RunSpeed는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D4:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="MaxMana는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="E4:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="ManaRegen는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="JumpPower는 0보다 커야 합니다." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/Content/Data/PlayerBaseStat.xlsx
+++ b/Content/Data/PlayerBaseStat.xlsx
@@ -460,50 +460,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hp</t>
+          <t>MaxHP</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>HPRegen</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>HPRegenDelay</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>WalkSpeed</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>RunSpeed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>MaxMana</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ManaRegen</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>JumpPower</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -527,20 +539,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>[float]</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[float]</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>[int]</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>[float]</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>[float]</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>[string]</t>
         </is>
@@ -549,35 +571,45 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>체력</t>
+          <t>최대 체력</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>초당 체력 회복량</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>피격 후 체력회복 지연시간(초)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>걷기 이동속도</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>달리기 이동속도</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>최대 마나</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>초당 마나 회복량</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>점프력</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기획 메모(변환시 제외)</t>
         </is>
@@ -588,44 +620,56 @@
         <v>100</v>
       </c>
       <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>420</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>기본 스탯</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation sqref="A4:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="Hp는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+  <dataValidations count="8">
+    <dataValidation sqref="A4:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="MaxHP는 0보다 커야 합니다." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="B4:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="WalkSpeed는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+    <dataValidation sqref="B4:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="HPRegen는 0보다 커야 합니다." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="RunSpeed는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+    <dataValidation sqref="C4:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="HPRegenDelay는 0보다 커야 합니다." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="D4:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="MaxMana는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+    <dataValidation sqref="D4:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="WalkSpeed는 0보다 커야 합니다." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="ManaRegen는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+    <dataValidation sqref="E4:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="RunSpeed는 0보다 커야 합니다." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="JumpPower는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+    <dataValidation sqref="F4:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="MaxMana는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="ManaRegen는 0보다 커야 합니다." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H4:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="범위 오류" error="JumpPower는 0보다 커야 합니다." type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/Content/Data/PlayerBaseStat.xlsx
+++ b/Content/Data/PlayerBaseStat.xlsx
@@ -524,7 +524,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>[int]</t>
+          <t>[float]</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>[int]</t>
+          <t>[float]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
